--- a/PythonWorkingScripts_InputData/UI/Assessment/Grid_Actions_input.xlsx
+++ b/PythonWorkingScripts_InputData/UI/Assessment/Grid_Actions_input.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="10580"/>
+    <workbookView windowWidth="28800" windowHeight="10740" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="assessment_grid_actions" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="229">
   <si>
     <t>TestCases</t>
   </si>
@@ -242,6 +242,9 @@
     <t>View Registration Link</t>
   </si>
   <si>
+    <t>View Sent Reminders Info</t>
+  </si>
+  <si>
     <t>Assessment applicants (Not Attended)</t>
   </si>
   <si>
@@ -261,6 +264,9 @@
   </si>
   <si>
     <t>Send Reminder</t>
+  </si>
+  <si>
+    <t>Send Manual Reminder</t>
   </si>
   <si>
     <t>Assessment applicants (Attending)</t>
@@ -1839,7 +1845,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" customFormat="1" spans="1:31">
+    <row r="3" customFormat="1" spans="1:32">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1933,10 +1939,13 @@
       <c r="AE3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="4" customFormat="1" spans="1:25">
+      <c r="AF3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:27">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B4">
         <v>21193</v>
@@ -1960,13 +1969,13 @@
         <v>51</v>
       </c>
       <c r="I4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L4" t="s">
         <v>57</v>
@@ -1975,19 +1984,19 @@
         <v>58</v>
       </c>
       <c r="N4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O4" t="s">
         <v>60</v>
       </c>
       <c r="P4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q4" t="s">
         <v>12</v>
       </c>
       <c r="R4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S4" t="s">
         <v>28</v>
@@ -2010,10 +2019,16 @@
       <c r="Y4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:30">
+      <c r="Z4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:32">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B5">
         <v>21193</v>
@@ -2043,7 +2058,7 @@
         <v>56</v>
       </c>
       <c r="K5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L5" t="s">
         <v>57</v>
@@ -2052,16 +2067,16 @@
         <v>58</v>
       </c>
       <c r="N5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P5" t="s">
         <v>60</v>
       </c>
       <c r="Q5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R5" t="s">
         <v>12</v>
@@ -2073,7 +2088,7 @@
         <v>62</v>
       </c>
       <c r="U5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="V5" t="s">
         <v>63</v>
@@ -2102,10 +2117,16 @@
       <c r="AD5" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="6" customFormat="1" spans="1:28">
+      <c r="AE5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:30">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B6">
         <v>21193</v>
@@ -2126,7 +2147,7 @@
         <v>49</v>
       </c>
       <c r="H6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I6" t="s">
         <v>51</v>
@@ -2138,7 +2159,7 @@
         <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M6" t="s">
         <v>57</v>
@@ -2147,13 +2168,13 @@
         <v>58</v>
       </c>
       <c r="O6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P6" t="s">
         <v>60</v>
       </c>
       <c r="Q6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R6" t="s">
         <v>12</v>
@@ -2188,10 +2209,16 @@
       <c r="AB6" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="7" spans="1:37">
+      <c r="AC6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B7">
         <v>21193</v>
@@ -2215,7 +2242,7 @@
         <v>50</v>
       </c>
       <c r="I7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J7" t="s">
         <v>51</v>
@@ -2224,7 +2251,7 @@
         <v>52</v>
       </c>
       <c r="L7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M7" t="s">
         <v>54</v>
@@ -2245,7 +2272,7 @@
         <v>31</v>
       </c>
       <c r="S7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="T7" t="s">
         <v>59</v>
@@ -2263,16 +2290,16 @@
         <v>62</v>
       </c>
       <c r="Y7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Z7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AA7" t="s">
         <v>63</v>
       </c>
       <c r="AB7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AC7" t="s">
         <v>64</v>
@@ -2287,7 +2314,7 @@
         <v>44</v>
       </c>
       <c r="AG7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH7" t="s">
         <v>67</v>
@@ -2301,10 +2328,13 @@
       <c r="AK7" t="s">
         <v>46</v>
       </c>
+      <c r="AL7" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="8" customFormat="1" spans="1:47">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B8">
         <v>21381</v>
@@ -2403,7 +2433,7 @@
         <v>34</v>
       </c>
       <c r="AH8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI8" t="s">
         <v>35</v>
@@ -2445,9 +2475,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="1:26">
+    <row r="9" customFormat="1" spans="1:28">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B9">
         <v>21381</v>
@@ -2471,13 +2501,13 @@
         <v>51</v>
       </c>
       <c r="I9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L9" t="s">
         <v>57</v>
@@ -2486,19 +2516,19 @@
         <v>58</v>
       </c>
       <c r="N9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O9" t="s">
         <v>60</v>
       </c>
       <c r="P9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q9" t="s">
         <v>12</v>
       </c>
       <c r="R9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S9" t="s">
         <v>28</v>
@@ -2507,7 +2537,7 @@
         <v>64</v>
       </c>
       <c r="U9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="V9" t="s">
         <v>65</v>
@@ -2524,10 +2554,16 @@
       <c r="Z9" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" customFormat="1" spans="1:32">
+      <c r="AA9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:33">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B10">
         <v>21381</v>
@@ -2557,7 +2593,7 @@
         <v>52</v>
       </c>
       <c r="K10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L10" t="s">
         <v>54</v>
@@ -2581,7 +2617,7 @@
         <v>60</v>
       </c>
       <c r="S10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="T10" t="s">
         <v>61</v>
@@ -2596,7 +2632,7 @@
         <v>63</v>
       </c>
       <c r="X10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Y10" t="s">
         <v>64</v>
@@ -2622,10 +2658,13 @@
       <c r="AF10" t="s">
         <v>46</v>
       </c>
+      <c r="AG10" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="11" spans="1:33">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B11">
         <v>21193</v>
@@ -2694,7 +2733,7 @@
         <v>26</v>
       </c>
       <c r="X11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Y11" t="s">
         <v>29</v>
@@ -2703,13 +2742,13 @@
         <v>31</v>
       </c>
       <c r="AA11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AB11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AC11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AD11" t="s">
         <v>28</v>
@@ -2724,9 +2763,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:25">
       <c r="A12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B12">
         <v>21193</v>
@@ -2765,7 +2804,7 @@
         <v>55</v>
       </c>
       <c r="N12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="O12" t="s">
         <v>57</v>
@@ -2797,10 +2836,13 @@
       <c r="X12" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="13" spans="1:21">
+      <c r="Y12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
       <c r="A13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B13">
         <v>21193</v>
@@ -2824,13 +2866,13 @@
         <v>51</v>
       </c>
       <c r="I13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L13" t="s">
         <v>57</v>
@@ -2839,16 +2881,16 @@
         <v>58</v>
       </c>
       <c r="N13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P13" t="s">
         <v>12</v>
       </c>
       <c r="Q13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R13" t="s">
         <v>60</v>
@@ -2862,10 +2904,16 @@
       <c r="U13" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="14" spans="1:23">
+      <c r="V13" t="s">
+        <v>78</v>
+      </c>
+      <c r="W13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B14">
         <v>21193</v>
@@ -2892,10 +2940,10 @@
         <v>52</v>
       </c>
       <c r="J14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L14" t="s">
         <v>57</v>
@@ -2904,13 +2952,13 @@
         <v>58</v>
       </c>
       <c r="N14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q14" t="s">
         <v>12</v>
@@ -2919,7 +2967,7 @@
         <v>60</v>
       </c>
       <c r="S14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="T14" t="s">
         <v>66</v>
@@ -2933,10 +2981,16 @@
       <c r="W14" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="15" spans="1:21">
+      <c r="X14" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B15">
         <v>21193</v>
@@ -2957,7 +3011,7 @@
         <v>49</v>
       </c>
       <c r="H15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I15" t="s">
         <v>51</v>
@@ -2966,10 +3020,10 @@
         <v>52</v>
       </c>
       <c r="K15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M15" t="s">
         <v>57</v>
@@ -2978,10 +3032,10 @@
         <v>58</v>
       </c>
       <c r="O15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q15" t="s">
         <v>12</v>
@@ -2998,10 +3052,16 @@
       <c r="U15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="16" spans="1:28">
+      <c r="V15" t="s">
+        <v>78</v>
+      </c>
+      <c r="W15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B16">
         <v>21193</v>
@@ -3025,7 +3085,7 @@
         <v>50</v>
       </c>
       <c r="I16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J16" t="s">
         <v>51</v>
@@ -3034,7 +3094,7 @@
         <v>52</v>
       </c>
       <c r="L16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M16" t="s">
         <v>54</v>
@@ -3043,7 +3103,7 @@
         <v>55</v>
       </c>
       <c r="O16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="P16" t="s">
         <v>57</v>
@@ -3055,7 +3115,7 @@
         <v>31</v>
       </c>
       <c r="S16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="T16" t="s">
         <v>59</v>
@@ -3067,7 +3127,7 @@
         <v>60</v>
       </c>
       <c r="W16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="X16" t="s">
         <v>66</v>
@@ -3082,12 +3142,15 @@
         <v>46</v>
       </c>
       <c r="AB16" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
+        <v>92</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B17">
         <v>21193</v>
@@ -3108,7 +3171,7 @@
         <v>56</v>
       </c>
       <c r="H17" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I17" t="s">
         <v>61</v>
@@ -3120,7 +3183,7 @@
         <v>62</v>
       </c>
       <c r="L17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M17" t="s">
         <v>58</v>
@@ -3140,10 +3203,13 @@
       <c r="R17" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="S17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B18">
         <v>21193</v>
@@ -3164,10 +3230,10 @@
         <v>56</v>
       </c>
       <c r="H18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I18" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J18" t="s">
         <v>37</v>
@@ -3176,7 +3242,7 @@
         <v>62</v>
       </c>
       <c r="L18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M18" t="s">
         <v>58</v>
@@ -3193,10 +3259,16 @@
       <c r="Q18" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="19" spans="1:19">
+      <c r="R18" t="s">
+        <v>78</v>
+      </c>
+      <c r="S18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B19">
         <v>21193</v>
@@ -3217,10 +3289,10 @@
         <v>56</v>
       </c>
       <c r="H19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I19" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J19" t="s">
         <v>37</v>
@@ -3229,10 +3301,10 @@
         <v>62</v>
       </c>
       <c r="L19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N19" t="s">
         <v>58</v>
@@ -3252,10 +3324,16 @@
       <c r="S19" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="T19" t="s">
+        <v>78</v>
+      </c>
+      <c r="U19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B20">
         <v>21193</v>
@@ -3273,19 +3351,19 @@
         <v>7</v>
       </c>
       <c r="G20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I20" t="s">
         <v>12</v>
       </c>
       <c r="J20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L20" t="s">
         <v>58</v>
@@ -3302,10 +3380,16 @@
       <c r="P20" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="21" spans="1:19">
+      <c r="Q20" t="s">
+        <v>78</v>
+      </c>
+      <c r="R20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
       <c r="A21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B21">
         <v>21193</v>
@@ -3329,7 +3413,7 @@
         <v>53</v>
       </c>
       <c r="I21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J21" t="s">
         <v>61</v>
@@ -3341,7 +3425,7 @@
         <v>62</v>
       </c>
       <c r="M21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N21" t="s">
         <v>58</v>
@@ -3361,10 +3445,13 @@
       <c r="S21" t="s">
         <v>44</v>
       </c>
+      <c r="T21" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="22" spans="1:46">
       <c r="A22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B22">
         <v>21193</v>
@@ -3502,9 +3589,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" customFormat="1" spans="1:33">
+    <row r="23" customFormat="1" spans="1:34">
       <c r="A23" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B23">
         <v>21193</v>
@@ -3585,27 +3672,30 @@
         <v>69</v>
       </c>
       <c r="AB23" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AC23" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AD23" t="s">
         <v>46</v>
       </c>
       <c r="AE23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AF23" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AG23" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" spans="1:32">
+        <v>123</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" spans="1:34">
       <c r="A24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B24">
         <v>21193</v>
@@ -3635,7 +3725,7 @@
         <v>56</v>
       </c>
       <c r="K24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L24" t="s">
         <v>57</v>
@@ -3644,22 +3734,22 @@
         <v>58</v>
       </c>
       <c r="N24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P24" t="s">
         <v>60</v>
       </c>
       <c r="Q24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R24" t="s">
         <v>12</v>
       </c>
       <c r="S24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="T24" t="s">
         <v>63</v>
@@ -3686,24 +3776,30 @@
         <v>69</v>
       </c>
       <c r="AB24" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AC24" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AD24" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AE24" t="s">
         <v>46</v>
       </c>
       <c r="AF24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" spans="1:27">
+        <v>122</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" spans="1:29">
       <c r="A25" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B25">
         <v>21193</v>
@@ -3727,13 +3823,13 @@
         <v>51</v>
       </c>
       <c r="I25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L25" t="s">
         <v>57</v>
@@ -3742,19 +3838,19 @@
         <v>58</v>
       </c>
       <c r="N25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O25" t="s">
         <v>60</v>
       </c>
       <c r="P25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q25" t="s">
         <v>12</v>
       </c>
       <c r="R25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S25" t="s">
         <v>28</v>
@@ -3775,18 +3871,24 @@
         <v>69</v>
       </c>
       <c r="Y25" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Z25" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AA25" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="26" customFormat="1" spans="1:39">
+      <c r="AB25" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="1:40">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B26">
         <v>21193</v>
@@ -3810,7 +3912,7 @@
         <v>50</v>
       </c>
       <c r="I26" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J26" t="s">
         <v>51</v>
@@ -3819,7 +3921,7 @@
         <v>52</v>
       </c>
       <c r="L26" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M26" t="s">
         <v>54</v>
@@ -3837,7 +3939,7 @@
         <v>31</v>
       </c>
       <c r="R26" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="S26" t="s">
         <v>59</v>
@@ -3849,16 +3951,16 @@
         <v>61</v>
       </c>
       <c r="V26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="W26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="X26" t="s">
         <v>63</v>
       </c>
       <c r="Y26" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Z26" t="s">
         <v>64</v>
@@ -3873,7 +3975,7 @@
         <v>44</v>
       </c>
       <c r="AD26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AE26" t="s">
         <v>67</v>
@@ -3885,22 +3987,25 @@
         <v>69</v>
       </c>
       <c r="AH26" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AI26" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AJ26" t="s">
         <v>46</v>
       </c>
       <c r="AK26" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AL26" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AM26" t="s">
-        <v>121</v>
+        <v>123</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -3924,1015 +4029,1015 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B2">
         <v>3795</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B3">
         <v>3743</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B4">
         <v>14105</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L4" t="s">
         <v>38</v>
       </c>
       <c r="M4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B5">
         <v>14103</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I5" t="s">
         <v>38</v>
       </c>
       <c r="J5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B6">
         <v>147813</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B7">
         <v>147809</v>
       </c>
       <c r="C7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B8">
         <v>147807</v>
       </c>
       <c r="C8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B9">
         <v>147805</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B10">
         <v>147801</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I10" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B11">
         <v>147799</v>
       </c>
       <c r="C11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B12">
         <v>147797</v>
       </c>
       <c r="C12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B13">
         <v>147795</v>
       </c>
       <c r="C13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D13" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B14">
         <v>147793</v>
       </c>
       <c r="C14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E14" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B15">
         <v>147789</v>
       </c>
       <c r="C15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E15" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G15" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H15" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I15" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B16">
         <v>147787</v>
       </c>
       <c r="C16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E16" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G16" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H16" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I16" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J16" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K16" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B17">
         <v>147785</v>
       </c>
       <c r="C17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F17" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H17" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J17" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B18">
         <v>147783</v>
       </c>
       <c r="C18" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D18" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E18" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F18" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G18" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H18" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I18" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B19">
         <v>147781</v>
       </c>
       <c r="C19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E19" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F19" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G19" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H19" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B20">
         <v>147779</v>
       </c>
       <c r="C20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D20" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E20" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F20" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G20" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H20" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I20" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J20" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B21">
         <v>147771</v>
       </c>
       <c r="C21" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D21" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F21" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G21" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H21" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I21" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J21" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B22">
         <v>147763</v>
       </c>
       <c r="C22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D22" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E22" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F22" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G22" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H22" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I22" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J22" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K22" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L22" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B23">
         <v>147761</v>
       </c>
       <c r="C23" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D23" t="s">
+        <v>181</v>
+      </c>
+      <c r="E23" t="s">
+        <v>151</v>
+      </c>
+      <c r="F23" t="s">
+        <v>160</v>
+      </c>
+      <c r="G23" t="s">
+        <v>157</v>
+      </c>
+      <c r="H23" t="s">
+        <v>161</v>
+      </c>
+      <c r="I23" t="s">
+        <v>153</v>
+      </c>
+      <c r="J23" t="s">
+        <v>154</v>
+      </c>
+      <c r="K23" t="s">
         <v>179</v>
-      </c>
-      <c r="E23" t="s">
-        <v>149</v>
-      </c>
-      <c r="F23" t="s">
-        <v>158</v>
-      </c>
-      <c r="G23" t="s">
-        <v>155</v>
-      </c>
-      <c r="H23" t="s">
-        <v>159</v>
-      </c>
-      <c r="I23" t="s">
-        <v>151</v>
-      </c>
-      <c r="J23" t="s">
-        <v>152</v>
-      </c>
-      <c r="K23" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B24">
         <v>147759</v>
       </c>
       <c r="C24" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D24" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E24" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F24" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G24" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H24" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I24" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J24" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K24" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B25">
         <v>147757</v>
       </c>
       <c r="C25" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D25" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E25" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F25" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G25" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H25" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I25" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J25" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K25" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B26">
         <v>148425</v>
       </c>
       <c r="C26" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E26" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F26" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G26" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H26" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I26" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B27">
         <v>148343</v>
       </c>
       <c r="C27" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D27" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E27" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F27" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G27" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H27" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I27" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J27" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B28">
         <v>148341</v>
       </c>
       <c r="C28" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D28" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E28" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G28" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H28" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B29">
         <v>148339</v>
       </c>
       <c r="C29" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D29" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E29" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F29" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G29" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H29" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I29" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B30">
         <v>148337</v>
       </c>
       <c r="C30" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D30" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E30" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G30" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B31">
         <v>148335</v>
       </c>
       <c r="C31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D31" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E31" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F31" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G31" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B32">
         <v>148333</v>
       </c>
       <c r="C32" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D32" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E32" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F32" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G32" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H32" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B33">
         <v>148327</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B34">
         <v>148325</v>
       </c>
       <c r="C34" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D34" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E34" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F34" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G34" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H34" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I34" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J34" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -4944,7 +5049,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4952,12 +5057,12 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B2">
         <v>581</v>
@@ -4966,10 +5071,10 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -4981,30 +5086,36 @@
         <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>200</v>
+      </c>
+      <c r="M2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B3">
         <v>1571285</v>
       </c>
       <c r="C3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>51</v>
@@ -5016,7 +5127,7 @@
         <v>56</v>
       </c>
       <c r="H3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I3" t="s">
         <v>57</v>
@@ -5025,30 +5136,39 @@
         <v>58</v>
       </c>
       <c r="K3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M3" t="s">
         <v>12</v>
       </c>
       <c r="N3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>78</v>
+      </c>
+      <c r="R3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B4">
         <v>1571283</v>
       </c>
       <c r="C4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D4" t="s">
         <v>51</v>
@@ -5060,7 +5180,7 @@
         <v>56</v>
       </c>
       <c r="G4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H4" t="s">
         <v>57</v>
@@ -5069,45 +5189,54 @@
         <v>58</v>
       </c>
       <c r="J4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M4" t="s">
         <v>12</v>
       </c>
       <c r="N4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="P4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B5">
         <v>1566625</v>
       </c>
       <c r="C5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D5" t="s">
         <v>51</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H5" t="s">
         <v>57</v>
@@ -5116,33 +5245,42 @@
         <v>58</v>
       </c>
       <c r="J5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L5" t="s">
         <v>12</v>
       </c>
       <c r="M5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O5" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="P5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>78</v>
+      </c>
+      <c r="R5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B6">
         <v>1566605</v>
       </c>
       <c r="C6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D6" t="s">
         <v>51</v>
@@ -5151,175 +5289,184 @@
         <v>52</v>
       </c>
       <c r="F6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" t="s">
         <v>56</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>57</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>58</v>
       </c>
-      <c r="I6" t="s">
-        <v>202</v>
-      </c>
       <c r="J6" t="s">
+        <v>204</v>
+      </c>
+      <c r="K6" t="s">
         <v>65</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" t="s">
         <v>14</v>
       </c>
-      <c r="L6" t="s">
-        <v>207</v>
-      </c>
-      <c r="M6" t="s">
-        <v>87</v>
-      </c>
       <c r="N6" t="s">
-        <v>208</v>
+        <v>209</v>
+      </c>
+      <c r="O6" t="s">
+        <v>89</v>
+      </c>
+      <c r="P6" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B7">
         <v>1571285</v>
       </c>
       <c r="C7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" t="s">
+        <v>213</v>
+      </c>
+      <c r="G7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" t="s">
         <v>210</v>
-      </c>
-      <c r="F7" t="s">
-        <v>211</v>
-      </c>
-      <c r="G7" t="s">
-        <v>87</v>
-      </c>
-      <c r="H7" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B8">
         <v>1571283</v>
       </c>
       <c r="C8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E8" t="s">
+        <v>212</v>
+      </c>
+      <c r="F8" t="s">
+        <v>213</v>
+      </c>
+      <c r="G8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" t="s">
         <v>210</v>
-      </c>
-      <c r="F8" t="s">
-        <v>211</v>
-      </c>
-      <c r="G8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H8" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B9">
         <v>1566605</v>
       </c>
       <c r="C9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E9" t="s">
+        <v>212</v>
+      </c>
+      <c r="F9" t="s">
+        <v>213</v>
+      </c>
+      <c r="G9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" t="s">
         <v>210</v>
-      </c>
-      <c r="F9" t="s">
-        <v>211</v>
-      </c>
-      <c r="G9" t="s">
-        <v>87</v>
-      </c>
-      <c r="H9" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B10">
         <v>23349</v>
       </c>
       <c r="C10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B11">
         <v>23520</v>
       </c>
       <c r="C11" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G11" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B12">
         <v>111</v>
       </c>
       <c r="C12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E12" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
